--- a/data/Escenarios_DCH_costos_nuevos/Costo_fijo/Carga_on_board_fixed_3estaciones_P142kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_costos_nuevos/Costo_fijo/Carga_on_board_fixed_3estaciones_P142kW/elmo_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_costos_nuevos\Costo_fijo\Carga_on_board_fixed_3estaciones_P142kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB319741-BC47-4618-8137-AF117A606F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2F07CA-C196-473F-8C0B-BF884A5B5E65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3583,7 +3583,7 @@
         <v>380</v>
       </c>
       <c r="C3">
-        <v>42071</v>
+        <v>18669</v>
       </c>
       <c r="D3">
         <v>142</v>
